--- a/NCU_Womens_Master_ID_Mapping.xlsx
+++ b/NCU_Womens_Master_ID_Mapping.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,6 +26,11 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -54,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,32 +440,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>NV_Play_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>NV_Play_Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Match_Confidence</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sport80_ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sport80_Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sport80_Club</t>
         </is>

--- a/NCU_Womens_Master_ID_Mapping.xlsx
+++ b/NCU_Womens_Master_ID_Mapping.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F371"/>
+  <dimension ref="A1:F373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -12311,6 +12311,70 @@
         </is>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>85e351b3-c1e4-403e-ae0f-5e3ddd0f4c1a</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Sarah G</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Manual Match</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2021114791</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Sarah Gallagher</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Lisburn Cricket Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>e87e107e-cfa4-4381-b56f-a4058aa546ef</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Jia Kava</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Exact Match</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>3000003361</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Jia Kava</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Holywood Cricket Club 1881</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
